--- a/api/clv1/codelist/OrganisationRegistrationAgency.xlsx
+++ b/api/clv1/codelist/OrganisationRegistrationAgency.xlsx
@@ -2586,7 +2586,7 @@
     <t>TZ</t>
   </si>
   <si>
-    <t>Tanzania, United Republic of</t>
+    <t>Tanzania, the United Republic of</t>
   </si>
   <si>
     <t>TZ-TRA</t>
